--- a/regist_confirm.php  単体テスト仕様書.xlsx
+++ b/regist_confirm.php  単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
   <si>
     <t>テスト区分</t>
   </si>
@@ -43,85 +43,155 @@
     <t>環境（PC/スマホ、ブラウザ、OS</t>
   </si>
   <si>
-    <t>画面表示（正常）</t>
-  </si>
-  <si>
-    <t>regist.phpで全項目正常入力</t>
-  </si>
-  <si>
-    <t>入力値が正しく表示される</t>
-  </si>
-  <si>
-    <t>セッションチェック</t>
-  </si>
-  <si>
-    <t>セッションなし</t>
-  </si>
-  <si>
-    <t>regist.phpへリダイレクトされる</t>
-  </si>
-  <si>
-    <t>名前（姓）表示</t>
-  </si>
-  <si>
-    <t>山田</t>
-  </si>
-  <si>
-    <t>「山田」と表示される</t>
-  </si>
-  <si>
-    <t>名前（名）表示</t>
-  </si>
-  <si>
-    <t>太郎</t>
-  </si>
-  <si>
-    <t>「太郎」と表示される</t>
-  </si>
-  <si>
-    <t>カナ（姓）表示</t>
-  </si>
-  <si>
-    <t>ヤマダ</t>
-  </si>
-  <si>
-    <t>「ヤマダ」と表示される</t>
-  </si>
-  <si>
-    <t>カナ（名）表示</t>
-  </si>
-  <si>
-    <t>タロウ</t>
-  </si>
-  <si>
-    <t>「タロウ」と表示される</t>
-  </si>
-  <si>
-    <t>メール表示</t>
-  </si>
-  <si>
-    <t>test@test.com</t>
-  </si>
-  <si>
-    <t>確認画面表示</t>
-  </si>
-  <si>
-    <t>正しく表示される</t>
+    <t>入力形式チェック</t>
+  </si>
+  <si>
+    <t>名前（姓）表示（漢字）</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）を入力時に漢字で値を入力する。
+⑤名前（姓）以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>入力した名前（姓）（漢字）が表示される</t>
+  </si>
+  <si>
+    <t>名前（姓）表示（英字）</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）を入力時に英字で値を入力する。
+⑤名前（姓）以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>入力した名前（姓）（英字）が表示される</t>
+  </si>
+  <si>
+    <t>名前（姓）表示（ひらがな）</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）を入力時にひらがなで値を入力する。
+⑤名前（姓）以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>入力した名前（姓）（ひらがな）が表示される</t>
+  </si>
+  <si>
+    <t>名前（名）表示（漢字）</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（名）を入力時に漢字で値を入力する。
+⑤名前（名）以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>入力した名前（名）（漢字）が表示される</t>
+  </si>
+  <si>
+    <t>名前（名）表示（英字）</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（名）を入力時に英字で値を入力する。
+⑤名前（名）以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>入力した名前（名）表示（英字）が表示される</t>
+  </si>
+  <si>
+    <t>名前（名）表示（ひらがな）</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（名）を入力時にひらがなで値を入力する。
+⑤名前（名）以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>カナ（姓）表示（カタカナ）</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（姓）を入力時にカタカナで値を入力する。
+⑤カナ（姓）以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>入力したカナ（姓）表示（カタカナ）が表示される</t>
+  </si>
+  <si>
+    <t>カナ（名）表示（カタカナ）</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（姓）を入力時にカタカナで値を入力する。
+⑤カナ（名）表示以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>入力したカナ（名）表示（カタカナ）が表示される</t>
+  </si>
+  <si>
+    <t>メールアドレス表示</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④メールアドレスを入力時にカタカナで値を入力する。
+⑤メールアドレス表示以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>入力したメールアドレスが表示される</t>
   </si>
   <si>
     <t>パスワード表示</t>
   </si>
   <si>
-    <t>abc123</t>
-  </si>
-  <si>
-    <t>●●●●●●と表示される</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④任意のパスワードを入力する。
+⑤パスワード以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>●●●●●●とのような、パスワードが黒字で表示される</t>
   </si>
   <si>
     <t>性別表示（男）</t>
   </si>
   <si>
-    <t>gender=0</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④性別を男と入力する。
+⑤パスワード以外の欄に値を入力する。
+⑥「確認する」押下</t>
   </si>
   <si>
     <t>「男」と表示される</t>
@@ -130,7 +200,12 @@
     <t>性別表示（女）</t>
   </si>
   <si>
-    <t>gender=1</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④性別を女と入力する。
+⑤パスワード以外の欄に値を入力する。
+⑥「確認する」押下</t>
   </si>
   <si>
     <t>「女」と表示される</t>
@@ -139,25 +214,68 @@
     <t>郵便番号表示</t>
   </si>
   <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④郵便番号を入力する。
+⑤郵便番号以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>入力した郵便番号が表示される</t>
+  </si>
+  <si>
     <t>都道府県表示</t>
   </si>
   <si>
-    <t>東京都</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④都道府県を選択する。
+⑤都道府県以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>選択した都道府県が表示される</t>
   </si>
   <si>
     <t>市区町村表示</t>
   </si>
   <si>
-    <t>渋谷区</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④市区町村を選択する。
+⑤市区町村以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>選択した市区町村が表示される</t>
   </si>
   <si>
     <t>番地表示</t>
   </si>
   <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④番地を入力する。
+⑤番地以外の欄に値を入力する。
+⑥「確認する」押下</t>
+  </si>
+  <si>
+    <t>選択した番地が表示される</t>
+  </si>
+  <si>
     <t>権限表示（一般）</t>
   </si>
   <si>
-    <t>authority=0</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④権限を一般を選択する。
+⑤権限以外の欄に値を入力する。
+⑥「確認する」押下</t>
   </si>
   <si>
     <t>「一般」と表示される</t>
@@ -166,7 +284,12 @@
     <t>権限表示（管理者）</t>
   </si>
   <si>
-    <t>authority=1</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④権限を管理者を選択する。
+⑤権限以外の欄に値を入力する。
+⑥「確認する」押下</t>
   </si>
   <si>
     <t>「管理者」と表示される</t>
@@ -175,49 +298,38 @@
     <t>前に戻るボタン</t>
   </si>
   <si>
-    <t>「前に戻る」押下</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④「前に戻る」押下</t>
   </si>
   <si>
     <t>regist.phpへ遷移する</t>
   </si>
   <si>
-    <t>入力保持確認</t>
-  </si>
-  <si>
-    <t>regist.php確認</t>
-  </si>
-  <si>
-    <t>入力値が保持されている</t>
-  </si>
-  <si>
-    <t>登録ボタン（正常）</t>
-  </si>
-  <si>
-    <t>正常入力済
-「登録する」押下</t>
+    <t>登録完了</t>
+  </si>
+  <si>
+    <t>登録ボタン</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④項目を入力する
+⑤「確認する」押下
+⑥確認画面の表示が出たことを確認する。
+⑦</t>
   </si>
   <si>
     <t>完了画面へ遷移しDB登録される</t>
-  </si>
-  <si>
-    <t>DBエラー</t>
-  </si>
-  <si>
-    <t>DB停止状態
-「登録する」押下</t>
-  </si>
-  <si>
-    <t>「エラーが発生したためアカウント登録できません。」と赤字表示</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-m-d"/>
-  </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -238,6 +350,7 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -253,7 +366,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border/>
     <border>
       <left style="thin">
@@ -269,11 +382,41 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -289,7 +432,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -297,12 +442,9 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -522,8 +664,8 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="16.5"/>
     <col customWidth="1" min="3" max="3" width="25.88"/>
-    <col customWidth="1" min="4" max="4" width="25.63"/>
-    <col customWidth="1" min="5" max="5" width="32.25"/>
+    <col customWidth="1" min="4" max="4" width="36.25"/>
+    <col customWidth="1" min="5" max="5" width="48.38"/>
     <col customWidth="1" min="6" max="6" width="13.38"/>
     <col customWidth="1" min="10" max="10" width="20.38"/>
   </cols>
@@ -578,424 +720,415 @@
       <c r="AA1" s="4"/>
     </row>
     <row r="2">
-      <c r="A2" s="5"/>
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="B2" s="6">
         <v>1.0</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
+      <c r="D2" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="E2" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="7"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3">
-      <c r="A3" s="5"/>
+      <c r="A3" s="10"/>
       <c r="B3" s="6">
         <v>2.0</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="D3" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="6">
         <v>3.0</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="7" t="s">
         <v>17</v>
       </c>
+      <c r="D4" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="E4" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
     </row>
     <row r="5">
-      <c r="A5" s="5"/>
+      <c r="A5" s="10"/>
       <c r="B5" s="6">
         <v>4.0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
+      <c r="D5" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="E5" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="7"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6">
-      <c r="A6" s="5"/>
+      <c r="A6" s="10"/>
       <c r="B6" s="6">
         <v>5.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>24</v>
       </c>
+      <c r="E6" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="F6" s="7"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
     </row>
     <row r="7">
-      <c r="A7" s="5"/>
+      <c r="A7" s="10"/>
       <c r="B7" s="6">
         <v>6.0</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="F7" s="7"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8">
-      <c r="A8" s="5"/>
+      <c r="A8" s="10"/>
       <c r="B8" s="6">
         <v>7.0</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="F8" s="7"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="5"/>
+      <c r="A9" s="10"/>
       <c r="B9" s="6">
         <v>8.0</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9"/>
+      <c r="D9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="F9" s="7"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10">
-      <c r="A10" s="5"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="6">
         <v>9.0</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="8" t="s">
         <v>34</v>
       </c>
+      <c r="D10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="F10" s="7"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="5"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="6">
         <v>10.0</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F11" s="7"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12">
-      <c r="A12" s="5"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="6">
         <v>11.0</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="5"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="6">
         <v>12.0</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1234567.0</v>
+        <v>43</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F13" s="7"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="5"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="6">
         <v>13.0</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>31</v>
+        <v>46</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="F14" s="7"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="5"/>
+      <c r="A15" s="10"/>
       <c r="B15" s="7">
         <v>14.0</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>31</v>
+        <v>49</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="F15" s="7"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="5"/>
+      <c r="A16" s="10"/>
       <c r="B16" s="7">
         <v>15.0</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="10">
-        <v>36892.0</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>31</v>
+        <v>52</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="F16" s="7"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="5"/>
+      <c r="A17" s="10"/>
       <c r="B17" s="7">
         <v>16.0</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>49</v>
+        <v>55</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="F17" s="7"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="5"/>
+      <c r="A18" s="10"/>
       <c r="B18" s="7">
         <v>17.0</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>51</v>
+        <v>58</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F18" s="7"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
     </row>
     <row r="19">
-      <c r="A19" s="5"/>
+      <c r="A19" s="10"/>
       <c r="B19" s="7">
         <v>18.0</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>54</v>
+        <v>61</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F19" s="7"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="20">
-      <c r="A20" s="5"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="7">
         <v>19.0</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>57</v>
+        <v>64</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F20" s="7"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
     </row>
     <row r="21">
-      <c r="A21" s="5"/>
+      <c r="A21" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="B21" s="7">
         <v>20.0</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>60</v>
+        <v>68</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F21" s="7"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5"/>
-      <c r="B22" s="7">
-        <v>21.0</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A20"/>
+  </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="I2:I18 F2:F22">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F21 I2:I21">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/regist_confirm.php  単体テスト仕様書.xlsx
+++ b/regist_confirm.php  単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="74">
   <si>
     <t>テスト区分</t>
   </si>
@@ -58,6 +58,15 @@
   </si>
   <si>
     <t>入力した名前（姓）（漢字）が表示される</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>早川</t>
+  </si>
+  <si>
+    <t>PC、ブラウザ</t>
   </si>
   <si>
     <t>名前（姓）表示（英字）</t>
@@ -329,6 +338,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <sz val="10.0"/>
@@ -416,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -442,7 +454,15 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
@@ -735,393 +755,553 @@
       <c r="E2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="10"/>
+      <c r="A3" s="12"/>
       <c r="B3" s="6">
         <v>2.0</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
+        <v>19</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="10"/>
+      <c r="A4" s="12"/>
       <c r="B4" s="6">
         <v>3.0</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
+        <v>22</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="10"/>
+      <c r="A5" s="12"/>
       <c r="B5" s="6">
         <v>4.0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
+        <v>25</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="10"/>
+      <c r="A6" s="12"/>
       <c r="B6" s="6">
         <v>5.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10"/>
+      <c r="A7" s="12"/>
       <c r="B7" s="6">
         <v>6.0</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10"/>
+      <c r="A8" s="12"/>
       <c r="B8" s="6">
         <v>7.0</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+        <v>33</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10"/>
+      <c r="A9" s="12"/>
       <c r="B9" s="6">
         <v>8.0</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10"/>
+      <c r="A10" s="12"/>
       <c r="B10" s="6">
         <v>9.0</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+        <v>39</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="6">
         <v>10.0</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+        <v>42</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10"/>
+      <c r="A12" s="12"/>
       <c r="B12" s="6">
         <v>11.0</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+        <v>45</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="6">
         <v>12.0</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+        <v>48</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10"/>
+      <c r="A14" s="12"/>
       <c r="B14" s="6">
         <v>13.0</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+        <v>51</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="10"/>
+      <c r="A15" s="12"/>
       <c r="B15" s="7">
         <v>14.0</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+        <v>54</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10"/>
+      <c r="A16" s="12"/>
       <c r="B16" s="7">
         <v>15.0</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+        <v>57</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="10"/>
+      <c r="A17" s="12"/>
       <c r="B17" s="7">
         <v>16.0</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+        <v>60</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I17" s="11"/>
+      <c r="J17" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="10"/>
+      <c r="A18" s="12"/>
       <c r="B18" s="7">
         <v>17.0</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+        <v>63</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="10"/>
+      <c r="A19" s="12"/>
       <c r="B19" s="7">
         <v>18.0</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+        <v>66</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I19" s="11"/>
+      <c r="J19" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="11"/>
+      <c r="A20" s="13"/>
       <c r="B20" s="7">
         <v>19.0</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+        <v>69</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I20" s="11"/>
+      <c r="J20" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B21" s="7">
         <v>20.0</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="10">
+        <v>46099.0</v>
+      </c>
+      <c r="I21" s="11"/>
+      <c r="J21" s="9" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/regist_confirm.php  単体テスト仕様書.xlsx
+++ b/regist_confirm.php  単体テスト仕様書.xlsx
@@ -762,7 +762,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="9" t="s">
@@ -790,7 +790,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I3" s="11"/>
       <c r="J3" s="9" t="s">
@@ -818,7 +818,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I4" s="11"/>
       <c r="J4" s="9" t="s">
@@ -846,7 +846,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I5" s="11"/>
       <c r="J5" s="9" t="s">
@@ -874,7 +874,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I6" s="11"/>
       <c r="J6" s="9" t="s">
@@ -902,7 +902,7 @@
         <v>15</v>
       </c>
       <c r="H7" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I7" s="11"/>
       <c r="J7" s="9" t="s">
@@ -930,7 +930,7 @@
         <v>15</v>
       </c>
       <c r="H8" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I8" s="11"/>
       <c r="J8" s="9" t="s">
@@ -958,7 +958,7 @@
         <v>15</v>
       </c>
       <c r="H9" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="9" t="s">
@@ -986,7 +986,7 @@
         <v>15</v>
       </c>
       <c r="H10" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I10" s="11"/>
       <c r="J10" s="9" t="s">
@@ -1014,7 +1014,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I11" s="11"/>
       <c r="J11" s="9" t="s">
@@ -1042,7 +1042,7 @@
         <v>15</v>
       </c>
       <c r="H12" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I12" s="11"/>
       <c r="J12" s="9" t="s">
@@ -1070,7 +1070,7 @@
         <v>15</v>
       </c>
       <c r="H13" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I13" s="11"/>
       <c r="J13" s="9" t="s">
@@ -1098,7 +1098,7 @@
         <v>15</v>
       </c>
       <c r="H14" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I14" s="11"/>
       <c r="J14" s="9" t="s">
@@ -1126,7 +1126,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I15" s="11"/>
       <c r="J15" s="9" t="s">
@@ -1154,7 +1154,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I16" s="11"/>
       <c r="J16" s="9" t="s">
@@ -1182,7 +1182,7 @@
         <v>15</v>
       </c>
       <c r="H17" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I17" s="11"/>
       <c r="J17" s="9" t="s">
@@ -1210,7 +1210,7 @@
         <v>15</v>
       </c>
       <c r="H18" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="9" t="s">
@@ -1238,7 +1238,7 @@
         <v>15</v>
       </c>
       <c r="H19" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I19" s="11"/>
       <c r="J19" s="9" t="s">
@@ -1266,7 +1266,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I20" s="11"/>
       <c r="J20" s="9" t="s">
@@ -1296,7 +1296,7 @@
         <v>15</v>
       </c>
       <c r="H21" s="10">
-        <v>46099.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I21" s="11"/>
       <c r="J21" s="9" t="s">
